--- a/tpl/tpl-base.xlsx
+++ b/tpl/tpl-base.xlsx
@@ -865,7 +865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1120,6 +1120,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2445,15 +2460,15 @@
         <v>140.4</v>
       </c>
       <c r="O5" s="30" t="n"/>
-      <c r="P5" s="81">
+      <c r="P5" s="88">
         <f>IF(AT5&gt;=0.9,AT5,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="81">
+      <c r="Q5" s="88">
         <f>IF(AND(AT5&lt;0.9,AT5&gt;0.4),AT5,"")</f>
         <v/>
       </c>
-      <c r="R5" s="81">
+      <c r="R5" s="88">
         <f>IF(AT5&lt;=0.4,AT5,"")</f>
         <v/>
       </c>
@@ -2489,25 +2504,25 @@
         <f>IF(AT5&gt;=0.9,N5,"")</f>
         <v/>
       </c>
-      <c r="AK5" s="82" t="n"/>
+      <c r="AK5" s="88" t="n"/>
       <c r="AL5" s="82">
         <f>IF(AT5&gt;=0.9,N5,"")</f>
         <v/>
       </c>
-      <c r="AM5" s="82" t="n"/>
+      <c r="AM5" s="88" t="n"/>
       <c r="AN5" s="82">
         <f>IF(AT5&gt;=0.9,N5,"")</f>
         <v/>
       </c>
-      <c r="AO5" s="82" t="n"/>
+      <c r="AO5" s="88" t="n"/>
       <c r="AP5" s="82">
         <f>IF(AT5&gt;=0.9,N5,"")</f>
         <v/>
       </c>
-      <c r="AQ5" s="82" t="n"/>
+      <c r="AQ5" s="88" t="n"/>
       <c r="AR5" s="82" t="n"/>
       <c r="AS5" s="82" t="n"/>
-      <c r="AT5" s="81" t="n">
+      <c r="AT5" s="88" t="n">
         <v>0.1</v>
       </c>
       <c r="AU5" s="79" t="n">
@@ -3015,15 +3030,15 @@
       <c r="N5" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="O5" s="56">
+      <c r="O5" s="89">
         <f>IF(AP5&gt;=0.9,AP5,"")</f>
         <v/>
       </c>
-      <c r="P5" s="56">
+      <c r="P5" s="89">
         <f>IF(AND(AP5&lt;0.9,AP5&gt;0.4),AP5,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="56">
+      <c r="Q5" s="89">
         <f>IF(AP5&lt;=0.4,AP5,"")</f>
         <v/>
       </c>
@@ -3072,22 +3087,22 @@
         <f>IF(AP5&gt;=0.9,N5,"")</f>
         <v/>
       </c>
-      <c r="AG5" s="44" t="n"/>
+      <c r="AG5" s="89" t="n"/>
       <c r="AH5" s="44">
         <f>IF(AP5&gt;=0.9,N5,"")</f>
         <v/>
       </c>
-      <c r="AI5" s="44" t="n"/>
+      <c r="AI5" s="89" t="n"/>
       <c r="AJ5" s="44" t="n"/>
-      <c r="AK5" s="44" t="n"/>
+      <c r="AK5" s="89" t="n"/>
       <c r="AL5" s="21">
         <f>IF(AP5&gt;=0.9,N5,"")</f>
         <v/>
       </c>
-      <c r="AM5" s="21" t="n"/>
+      <c r="AM5" s="90" t="n"/>
       <c r="AN5" s="21" t="n"/>
       <c r="AO5" s="21" t="n"/>
-      <c r="AP5" s="57" t="n">
+      <c r="AP5" s="90" t="n">
         <v>0.91</v>
       </c>
       <c r="AQ5" s="41" t="n">
@@ -3776,15 +3791,15 @@
       <c r="T5" s="30" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="U5" s="31">
+      <c r="U5" s="91">
         <f>IF(BG5&gt;=0.9,BG5,"")</f>
         <v/>
       </c>
-      <c r="V5" s="31">
+      <c r="V5" s="91">
         <f>IF(AND(BG5&lt;0.9,BG5&gt;0.4),BG5,"")</f>
         <v/>
       </c>
-      <c r="W5" s="31">
+      <c r="W5" s="91">
         <f>IF(BG5&lt;=0.4,BG5,"")</f>
         <v/>
       </c>
@@ -3830,22 +3845,22 @@
         <f>IF(BG5&gt;=0.9,S5,"")</f>
         <v/>
       </c>
-      <c r="AX5" s="32" t="n"/>
+      <c r="AX5" s="92" t="n"/>
       <c r="AY5" s="32">
         <f>IF(BG5&gt;=0.9,S5,"")</f>
         <v/>
       </c>
-      <c r="AZ5" s="32" t="n"/>
+      <c r="AZ5" s="92" t="n"/>
       <c r="BA5" s="32" t="n"/>
-      <c r="BB5" s="32" t="n"/>
+      <c r="BB5" s="92" t="n"/>
       <c r="BC5" s="16">
         <f>IF(BG5&gt;=0.9,S5,"")</f>
         <v/>
       </c>
-      <c r="BD5" s="16" t="n"/>
+      <c r="BD5" s="91" t="n"/>
       <c r="BE5" s="16" t="n"/>
       <c r="BF5" s="16" t="n"/>
-      <c r="BG5" s="31" t="n">
+      <c r="BG5" s="91" t="n">
         <v>0.9</v>
       </c>
       <c r="BH5" s="30" t="n">
